--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:L6"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -405,19 +405,12 @@
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,43 +433,22 @@
         <v>currentPrice</v>
       </c>
       <c r="G1" t="str">
-        <v>change24h</v>
+        <v>notes</v>
       </c>
       <c r="H1" t="str">
-        <v>notes</v>
+        <v>accountType</v>
       </c>
       <c r="I1" t="str">
-        <v>accountType</v>
+        <v>accountName</v>
       </c>
       <c r="J1" t="str">
-        <v>accountName</v>
+        <v>costBasis</v>
       </c>
       <c r="K1" t="str">
-        <v>costBasis</v>
+        <v>purchaseDate</v>
       </c>
       <c r="L1" t="str">
-        <v>purchaseDate</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Day 1</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Day 2</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Day 3</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Day 4</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Day 5</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Day 6</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Day 7</v>
+        <v>lastUpdated</v>
       </c>
     </row>
     <row r="2">
@@ -498,44 +470,23 @@
       <c r="F2">
         <v>242.3</v>
       </c>
-      <c r="G2">
-        <v>1.8</v>
+      <c r="G2" t="str">
+        <v>Long-term hold. Services revenue accelerating.</v>
       </c>
       <c r="H2" t="str">
-        <v>Long-term hold. Services revenue accelerating.</v>
+        <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="J2" t="str">
         <v>Schwab Brokerage</v>
       </c>
-      <c r="K2">
+      <c r="J2">
         <v>26775</v>
       </c>
+      <c r="K2" t="str">
+        <v>2023-03-15</v>
+      </c>
       <c r="L2" t="str">
-        <v>2023-03-15</v>
-      </c>
-      <c r="M2">
-        <v>235</v>
-      </c>
-      <c r="N2">
-        <v>238</v>
-      </c>
-      <c r="O2">
-        <v>236</v>
-      </c>
-      <c r="P2">
-        <v>240</v>
-      </c>
-      <c r="Q2">
-        <v>239</v>
-      </c>
-      <c r="R2">
-        <v>241</v>
-      </c>
-      <c r="S2">
-        <v>242.3</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="3">
@@ -557,44 +508,23 @@
       <c r="F3">
         <v>892.5</v>
       </c>
-      <c r="G3">
-        <v>3.2</v>
+      <c r="G3" t="str">
+        <v>AI infrastructure leader. High conviction.</v>
       </c>
       <c r="H3" t="str">
-        <v>AI infrastructure leader. High conviction.</v>
+        <v>roth-ira</v>
       </c>
       <c r="I3" t="str">
-        <v>roth-ira</v>
-      </c>
-      <c r="J3" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>38800</v>
       </c>
+      <c r="K3" t="str">
+        <v>2023-06-20</v>
+      </c>
       <c r="L3" t="str">
-        <v>2023-06-20</v>
-      </c>
-      <c r="M3">
-        <v>845</v>
-      </c>
-      <c r="N3">
-        <v>860</v>
-      </c>
-      <c r="O3">
-        <v>855</v>
-      </c>
-      <c r="P3">
-        <v>870</v>
-      </c>
-      <c r="Q3">
-        <v>878</v>
-      </c>
-      <c r="R3">
-        <v>885</v>
-      </c>
-      <c r="S3">
-        <v>892.5</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="4">
@@ -616,44 +546,23 @@
       <c r="F4">
         <v>445.8</v>
       </c>
-      <c r="G4">
-        <v>-0.5</v>
+      <c r="G4" t="str">
+        <v>Cloud + AI play. Azure growth strong.</v>
       </c>
       <c r="H4" t="str">
-        <v>Cloud + AI play. Azure growth strong.</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I4" t="str">
-        <v>traditional-401k</v>
-      </c>
-      <c r="J4" t="str">
         <v>Company 401(k)</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>31000</v>
       </c>
+      <c r="K4" t="str">
+        <v>2022-01-10</v>
+      </c>
       <c r="L4" t="str">
-        <v>2022-01-10</v>
-      </c>
-      <c r="M4">
-        <v>448</v>
-      </c>
-      <c r="N4">
-        <v>450</v>
-      </c>
-      <c r="O4">
-        <v>447</v>
-      </c>
-      <c r="P4">
-        <v>446</v>
-      </c>
-      <c r="Q4">
-        <v>445</v>
-      </c>
-      <c r="R4">
-        <v>446</v>
-      </c>
-      <c r="S4">
-        <v>445.8</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="5">
@@ -675,44 +584,23 @@
       <c r="F5">
         <v>385.2</v>
       </c>
-      <c r="G5">
-        <v>-2.1</v>
+      <c r="G5" t="str">
+        <v>Robotaxi catalyst pending. Volatile.</v>
       </c>
       <c r="H5" t="str">
-        <v>Robotaxi catalyst pending. Volatile.</v>
+        <v>taxable</v>
       </c>
       <c r="I5" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="J5" t="str">
         <v>Schwab Brokerage</v>
       </c>
-      <c r="K5">
+      <c r="J5">
         <v>11700</v>
       </c>
+      <c r="K5" t="str">
+        <v>2024-02-28</v>
+      </c>
       <c r="L5" t="str">
-        <v>2024-02-28</v>
-      </c>
-      <c r="M5">
-        <v>395</v>
-      </c>
-      <c r="N5">
-        <v>392</v>
-      </c>
-      <c r="O5">
-        <v>390</v>
-      </c>
-      <c r="P5">
-        <v>388</v>
-      </c>
-      <c r="Q5">
-        <v>387</v>
-      </c>
-      <c r="R5">
-        <v>386</v>
-      </c>
-      <c r="S5">
-        <v>385.2</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="6">
@@ -734,49 +622,28 @@
       <c r="F6">
         <v>228.6</v>
       </c>
-      <c r="G6">
-        <v>0.9</v>
+      <c r="G6" t="str">
+        <v>AWS margins expanding. Advertising segment growing.</v>
       </c>
       <c r="H6" t="str">
-        <v>AWS margins expanding. Advertising segment growing.</v>
+        <v>roth-ira</v>
       </c>
       <c r="I6" t="str">
-        <v>roth-ira</v>
-      </c>
-      <c r="J6" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="K6">
+      <c r="J6">
         <v>13050</v>
       </c>
+      <c r="K6" t="str">
+        <v>2023-09-05</v>
+      </c>
       <c r="L6" t="str">
-        <v>2023-09-05</v>
-      </c>
-      <c r="M6">
-        <v>224</v>
-      </c>
-      <c r="N6">
-        <v>225</v>
-      </c>
-      <c r="O6">
-        <v>226</v>
-      </c>
-      <c r="P6">
-        <v>225</v>
-      </c>
-      <c r="Q6">
-        <v>227</v>
-      </c>
-      <c r="R6">
-        <v>228</v>
-      </c>
-      <c r="S6">
-        <v>228.6</v>
+        <v>2026-02-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L14"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -453,25 +453,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>aapl</v>
+        <v>vti</v>
       </c>
       <c r="B2" t="str">
-        <v>Apple Inc.</v>
+        <v>Vanguard Total Stock Market ETF</v>
       </c>
       <c r="C2" t="str">
-        <v>AAPL</v>
+        <v>VTI</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E2">
-        <v>178.5</v>
+        <v>215</v>
       </c>
       <c r="F2">
-        <v>242.3</v>
+        <v>280</v>
       </c>
       <c r="G2" t="str">
-        <v>Long-term hold. Services revenue accelerating.</v>
+        <v>Core diversified holding. Funded by Anthropic tender offer proceeds (2024-2025). Tax-efficient broad market.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
@@ -480,112 +480,112 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J2">
-        <v>26775</v>
+        <v>258000</v>
       </c>
       <c r="K2" t="str">
-        <v>2023-03-15</v>
+        <v>2024-12-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>nvda</v>
+        <v>vxus</v>
       </c>
       <c r="B3" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C3" t="str">
-        <v>NVDA</v>
+        <v>VXUS</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <v>1500</v>
       </c>
       <c r="E3">
-        <v>485</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>892.5</v>
+        <v>60</v>
       </c>
       <c r="G3" t="str">
-        <v>AI infrastructure leader. High conviction.</v>
+        <v>International diversification. Foreign tax credit eligible.</v>
       </c>
       <c r="H3" t="str">
-        <v>roth-ira</v>
+        <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J3">
-        <v>38800</v>
+        <v>78000</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-06-20</v>
+        <v>2024-12-15</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>msft</v>
+        <v>qqq</v>
       </c>
       <c r="B4" t="str">
-        <v>Microsoft</v>
+        <v>Invesco QQQ Trust</v>
       </c>
       <c r="C4" t="str">
-        <v>MSFT</v>
+        <v>QQQ</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E4">
-        <v>310</v>
+        <v>385</v>
       </c>
       <c r="F4">
-        <v>445.8</v>
+        <v>530</v>
       </c>
       <c r="G4" t="str">
-        <v>Cloud + AI play. Azure growth strong.</v>
+        <v>Nasdaq-100 exposure. Tech-heavy tilt — comfortable given domain expertise.</v>
       </c>
       <c r="H4" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I4" t="str">
-        <v>Company 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J4">
-        <v>31000</v>
+        <v>96250</v>
       </c>
       <c r="K4" t="str">
-        <v>2022-01-10</v>
+        <v>2025-01-10</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>tsla</v>
+        <v>bnd</v>
       </c>
       <c r="B5" t="str">
-        <v>Tesla Inc.</v>
+        <v>Vanguard Total Bond Market ETF</v>
       </c>
       <c r="C5" t="str">
-        <v>TSLA</v>
+        <v>BND</v>
       </c>
       <c r="D5">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E5">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="F5">
-        <v>385.2</v>
+        <v>72</v>
       </c>
       <c r="G5" t="str">
-        <v>Robotaxi catalyst pending. Volatile.</v>
+        <v>Bond allocation for stability. Slight loss from rate hikes.</v>
       </c>
       <c r="H5" t="str">
         <v>taxable</v>
@@ -594,56 +594,360 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J5">
-        <v>11700</v>
+        <v>37000</v>
       </c>
       <c r="K5" t="str">
-        <v>2024-02-28</v>
+        <v>2025-03-01</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>amzn</v>
+        <v>aapl</v>
       </c>
       <c r="B6" t="str">
-        <v>Amazon</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C6" t="str">
-        <v>AMZN</v>
+        <v>AAPL</v>
       </c>
       <c r="D6">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="F6">
-        <v>228.6</v>
+        <v>242</v>
       </c>
       <c r="G6" t="str">
-        <v>AWS margins expanding. Advertising segment growing.</v>
+        <v>Long-term conviction hold. On-device AI play.</v>
       </c>
       <c r="H6" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Schwab Brokerage</v>
+      </c>
+      <c r="J6">
+        <v>27000</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2024-11-15</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>nvda</v>
+      </c>
+      <c r="B7" t="str">
+        <v>NVIDIA Corp.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>NVDA</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>490</v>
+      </c>
+      <c r="F7">
+        <v>892</v>
+      </c>
+      <c r="G7" t="str">
+        <v>AI infrastructure leader. High conviction — understands the compute moat deeply.</v>
+      </c>
+      <c r="H7" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Schwab Brokerage</v>
+      </c>
+      <c r="J7">
+        <v>24500</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2025-01-20</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>schd</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Schwab US Dividend Equity ETF</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SCHD</v>
+      </c>
+      <c r="D8">
+        <v>300</v>
+      </c>
+      <c r="E8">
+        <v>70</v>
+      </c>
+      <c r="F8">
+        <v>82</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Dividend ETF for passive income. Diversification from growth tilt.</v>
+      </c>
+      <c r="H8" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Schwab Brokerage</v>
+      </c>
+      <c r="J8">
+        <v>21000</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2025-06-01</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>voo-401k</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Vanguard S&amp;P 500 ETF</v>
+      </c>
+      <c r="C9" t="str">
+        <v>VOO</v>
+      </c>
+      <c r="D9">
+        <v>450</v>
+      </c>
+      <c r="E9">
+        <v>385</v>
+      </c>
+      <c r="F9">
+        <v>520</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Core 401(k) holding. DCA via payroll. No employer match at Anthropic.</v>
+      </c>
+      <c r="H9" t="str">
+        <v>traditional-401k</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Fidelity 401(k)</v>
+      </c>
+      <c r="J9">
+        <v>173250</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2022-02-01</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>vxus-401k</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Vanguard Total Intl Stock ETF</v>
+      </c>
+      <c r="C10" t="str">
+        <v>VXUS</v>
+      </c>
+      <c r="D10">
+        <v>400</v>
+      </c>
+      <c r="E10">
+        <v>52</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10" t="str">
+        <v>International diversification in 401(k).</v>
+      </c>
+      <c r="H10" t="str">
+        <v>traditional-401k</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Fidelity 401(k)</v>
+      </c>
+      <c r="J10">
+        <v>20800</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2022-02-01</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>bnd-401k</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Vanguard Total Bond Market ETF</v>
+      </c>
+      <c r="C11" t="str">
+        <v>BND</v>
+      </c>
+      <c r="D11">
+        <v>600</v>
+      </c>
+      <c r="E11">
+        <v>74</v>
+      </c>
+      <c r="F11">
+        <v>72</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Bond allocation in 401(k). Slight loss from rate hikes.</v>
+      </c>
+      <c r="H11" t="str">
+        <v>traditional-401k</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Fidelity 401(k)</v>
+      </c>
+      <c r="J11">
+        <v>44400</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2022-06-01</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>vti-roth</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Vanguard Total Stock Market ETF</v>
+      </c>
+      <c r="C12" t="str">
+        <v>VTI</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>225</v>
+      </c>
+      <c r="F12">
+        <v>280</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
+      </c>
+      <c r="H12" t="str">
         <v>roth-ira</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I12" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="J6">
-        <v>13050</v>
-      </c>
-      <c r="K6" t="str">
-        <v>2023-09-05</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-02-11</v>
+      <c r="J12">
+        <v>22500</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2023-01-15</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>nvda-roth</v>
+      </c>
+      <c r="B13" t="str">
+        <v>NVIDIA Corp.</v>
+      </c>
+      <c r="C13" t="str">
+        <v>NVDA</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>490</v>
+      </c>
+      <c r="F13">
+        <v>892</v>
+      </c>
+      <c r="G13" t="str">
+        <v>High-growth in Roth for tax-free gains. AI thesis.</v>
+      </c>
+      <c r="H13" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J13">
+        <v>7350</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2023-06-20</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>aapl-roth</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Apple Inc.</v>
+      </c>
+      <c r="C14" t="str">
+        <v>AAPL</v>
+      </c>
+      <c r="D14">
+        <v>35</v>
+      </c>
+      <c r="E14">
+        <v>180</v>
+      </c>
+      <c r="F14">
+        <v>242</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Long-term hold in Roth. Tax-free dividend growth.</v>
+      </c>
+      <c r="H14" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J14">
+        <v>6300</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2023-03-15</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -453,37 +453,37 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>vti</v>
+        <v>meta</v>
       </c>
       <c r="B2" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
+        <v>Meta Platforms</v>
       </c>
       <c r="C2" t="str">
-        <v>VTI</v>
+        <v>META</v>
       </c>
       <c r="D2">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="E2">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>280</v>
+        <v>595</v>
       </c>
       <c r="G2" t="str">
-        <v>Core diversified holding. Funded by Anthropic tender offer proceeds (2024-2025). Tax-efficient broad market.</v>
+        <v>Vested RSU from 6 years at Meta (E6). Now regular stock. Selling 10-15% annually to diversify. Concentrated position — plan multi-year drawdown.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>Schwab Brokerage</v>
+        <v>E*TRADE</v>
       </c>
       <c r="J2">
-        <v>258000</v>
+        <v>450000</v>
       </c>
       <c r="K2" t="str">
-        <v>2024-12-01</v>
+        <v>2018-06-01</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
@@ -491,37 +491,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>vxus</v>
+        <v>voo-401k</v>
       </c>
       <c r="B3" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Vanguard S&amp;P 500 ETF</v>
       </c>
       <c r="C3" t="str">
-        <v>VXUS</v>
+        <v>VOO</v>
       </c>
       <c r="D3">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E3">
-        <v>52</v>
+        <v>380</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>520</v>
       </c>
       <c r="G3" t="str">
-        <v>International diversification. Foreign tax credit eligible.</v>
+        <v>Core 401(k) holding. DCA via payroll. Google matches up to $9,500/yr.</v>
       </c>
       <c r="H3" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I3" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J3">
-        <v>78000</v>
+        <v>380000</v>
       </c>
       <c r="K3" t="str">
-        <v>2024-12-15</v>
+        <v>2020-01-10</v>
       </c>
       <c r="L3" t="str">
         <v>2026-02-12</v>
@@ -529,37 +529,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>qqq</v>
+        <v>vxus-401k</v>
       </c>
       <c r="B4" t="str">
-        <v>Invesco QQQ Trust</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C4" t="str">
-        <v>QQQ</v>
+        <v>VXUS</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="E4">
-        <v>385</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>530</v>
+        <v>60</v>
       </c>
       <c r="G4" t="str">
-        <v>Nasdaq-100 exposure. Tech-heavy tilt — comfortable given domain expertise.</v>
+        <v>International diversification in 401(k). ~7% of retirement allocation.</v>
       </c>
       <c r="H4" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I4" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J4">
-        <v>96250</v>
+        <v>36400</v>
       </c>
       <c r="K4" t="str">
-        <v>2025-01-10</v>
+        <v>2020-01-10</v>
       </c>
       <c r="L4" t="str">
         <v>2026-02-12</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bnd</v>
+        <v>bnd-401k</v>
       </c>
       <c r="B5" t="str">
         <v>Vanguard Total Bond Market ETF</v>
@@ -576,7 +576,7 @@
         <v>BND</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E5">
         <v>74</v>
@@ -585,19 +585,19 @@
         <v>72</v>
       </c>
       <c r="G5" t="str">
-        <v>Bond allocation for stability. Slight loss from rate hikes.</v>
+        <v>Bond allocation in 401(k). ~7% of retirement. Slight loss from rate hikes.</v>
       </c>
       <c r="H5" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I5" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J5">
-        <v>37000</v>
+        <v>44400</v>
       </c>
       <c r="K5" t="str">
-        <v>2025-03-01</v>
+        <v>2021-06-01</v>
       </c>
       <c r="L5" t="str">
         <v>2026-02-12</v>
@@ -605,25 +605,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>aapl</v>
+        <v>vti</v>
       </c>
       <c r="B6" t="str">
-        <v>Apple Inc.</v>
+        <v>Vanguard Total Stock Market ETF</v>
       </c>
       <c r="C6" t="str">
-        <v>AAPL</v>
+        <v>VTI</v>
       </c>
       <c r="D6">
-        <v>150</v>
+        <v>1800</v>
       </c>
       <c r="E6">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F6">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="G6" t="str">
-        <v>Long-term conviction hold. On-device AI play.</v>
+        <v>Core diversified holding. Funded partly by META stock sales. Tax-efficient broad market.</v>
       </c>
       <c r="H6" t="str">
         <v>taxable</v>
@@ -632,10 +632,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J6">
-        <v>27000</v>
+        <v>378000</v>
       </c>
       <c r="K6" t="str">
-        <v>2024-11-15</v>
+        <v>2022-03-15</v>
       </c>
       <c r="L6" t="str">
         <v>2026-02-12</v>
@@ -643,25 +643,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>nvda</v>
+        <v>qqq</v>
       </c>
       <c r="B7" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Invesco QQQ Trust</v>
       </c>
       <c r="C7" t="str">
-        <v>NVDA</v>
+        <v>QQQ</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="E7">
-        <v>490</v>
+        <v>380</v>
       </c>
       <c r="F7">
-        <v>892</v>
+        <v>530</v>
       </c>
       <c r="G7" t="str">
-        <v>AI infrastructure leader. High conviction — understands the compute moat deeply.</v>
+        <v>Nasdaq-100 exposure. Tech-heavy tilt alongside employer stock.</v>
       </c>
       <c r="H7" t="str">
         <v>taxable</v>
@@ -670,10 +670,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J7">
-        <v>24500</v>
+        <v>152000</v>
       </c>
       <c r="K7" t="str">
-        <v>2025-01-20</v>
+        <v>2023-01-20</v>
       </c>
       <c r="L7" t="str">
         <v>2026-02-12</v>
@@ -681,25 +681,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>schd</v>
+        <v>vxus</v>
       </c>
       <c r="B8" t="str">
-        <v>Schwab US Dividend Equity ETF</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C8" t="str">
-        <v>SCHD</v>
+        <v>VXUS</v>
       </c>
       <c r="D8">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E8">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F8">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="G8" t="str">
-        <v>Dividend ETF for passive income. Diversification from growth tilt.</v>
+        <v>International diversification in taxable. Foreign tax credit eligible.</v>
       </c>
       <c r="H8" t="str">
         <v>taxable</v>
@@ -708,10 +708,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>62400</v>
       </c>
       <c r="K8" t="str">
-        <v>2025-06-01</v>
+        <v>2022-06-15</v>
       </c>
       <c r="L8" t="str">
         <v>2026-02-12</v>
@@ -719,37 +719,37 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>voo-401k</v>
+        <v>vgt</v>
       </c>
       <c r="B9" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+        <v>Vanguard Information Technology ETF</v>
       </c>
       <c r="C9" t="str">
-        <v>VOO</v>
+        <v>VGT</v>
       </c>
       <c r="D9">
+        <v>150</v>
+      </c>
+      <c r="E9">
         <v>450</v>
       </c>
-      <c r="E9">
-        <v>385</v>
-      </c>
       <c r="F9">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="G9" t="str">
-        <v>Core 401(k) holding. DCA via payroll. No employer match at Anthropic.</v>
+        <v>Sector bet on tech. Overlaps with employer exposure — consider trimming.</v>
       </c>
       <c r="H9" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I9" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J9">
-        <v>173250</v>
+        <v>67500</v>
       </c>
       <c r="K9" t="str">
-        <v>2022-02-01</v>
+        <v>2023-06-01</v>
       </c>
       <c r="L9" t="str">
         <v>2026-02-12</v>
@@ -757,37 +757,37 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>vxus-401k</v>
+        <v>aapl</v>
       </c>
       <c r="B10" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C10" t="str">
-        <v>VXUS</v>
+        <v>AAPL</v>
       </c>
       <c r="D10">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E10">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="G10" t="str">
-        <v>International diversification in 401(k).</v>
+        <v>Long-term conviction hold. Services revenue accelerating.</v>
       </c>
       <c r="H10" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I10" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J10">
-        <v>20800</v>
+        <v>44500</v>
       </c>
       <c r="K10" t="str">
-        <v>2022-02-01</v>
+        <v>2023-03-15</v>
       </c>
       <c r="L10" t="str">
         <v>2026-02-12</v>
@@ -795,37 +795,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bnd-401k</v>
+        <v>nvda</v>
       </c>
       <c r="B11" t="str">
-        <v>Vanguard Total Bond Market ETF</v>
+        <v>NVIDIA Corp.</v>
       </c>
       <c r="C11" t="str">
-        <v>BND</v>
+        <v>NVDA</v>
       </c>
       <c r="D11">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>74</v>
+        <v>480</v>
       </c>
       <c r="F11">
-        <v>72</v>
+        <v>892</v>
       </c>
       <c r="G11" t="str">
-        <v>Bond allocation in 401(k). Slight loss from rate hikes.</v>
+        <v>AI infrastructure leader. High conviction position.</v>
       </c>
       <c r="H11" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I11" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J11">
-        <v>44400</v>
+        <v>38400</v>
       </c>
       <c r="K11" t="str">
-        <v>2022-06-01</v>
+        <v>2023-06-20</v>
       </c>
       <c r="L11" t="str">
         <v>2026-02-12</v>
@@ -833,37 +833,37 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>vti-roth</v>
+        <v>schd</v>
       </c>
       <c r="B12" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
+        <v>Schwab US Dividend Equity ETF</v>
       </c>
       <c r="C12" t="str">
-        <v>VTI</v>
+        <v>SCHD</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E12">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="F12">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="G12" t="str">
-        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
+        <v>Dividend ETF for passive income. Diversification from growth tilt.</v>
       </c>
       <c r="H12" t="str">
-        <v>roth-ira</v>
+        <v>taxable</v>
       </c>
       <c r="I12" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J12">
-        <v>22500</v>
+        <v>35000</v>
       </c>
       <c r="K12" t="str">
-        <v>2023-01-15</v>
+        <v>2023-09-01</v>
       </c>
       <c r="L12" t="str">
         <v>2026-02-12</v>
@@ -871,37 +871,37 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>nvda-roth</v>
+        <v>amzn</v>
       </c>
       <c r="B13" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Amazon</v>
       </c>
       <c r="C13" t="str">
-        <v>NVDA</v>
+        <v>AMZN</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>490</v>
+        <v>145</v>
       </c>
       <c r="F13">
-        <v>892</v>
+        <v>228</v>
       </c>
       <c r="G13" t="str">
-        <v>High-growth in Roth for tax-free gains. AI thesis.</v>
+        <v>AWS margins expanding. Advertising segment growing.</v>
       </c>
       <c r="H13" t="str">
-        <v>roth-ira</v>
+        <v>taxable</v>
       </c>
       <c r="I13" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J13">
-        <v>7350</v>
+        <v>17400</v>
       </c>
       <c r="K13" t="str">
-        <v>2023-06-20</v>
+        <v>2023-09-05</v>
       </c>
       <c r="L13" t="str">
         <v>2026-02-12</v>
@@ -909,45 +909,159 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>vnq</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Vanguard Real Estate ETF</v>
+      </c>
+      <c r="C14" t="str">
+        <v>VNQ</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>82.5</v>
+      </c>
+      <c r="F14">
+        <v>91.2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Broad REIT exposure. Dividend yield ~3.8%.</v>
+      </c>
+      <c r="H14" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Schwab Brokerage</v>
+      </c>
+      <c r="J14">
+        <v>16500</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>vti-roth</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Vanguard Total Stock Market ETF</v>
+      </c>
+      <c r="C15" t="str">
+        <v>VTI</v>
+      </c>
+      <c r="D15">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>220</v>
+      </c>
+      <c r="F15">
+        <v>280</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J15">
+        <v>44000</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2022-04-15</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>nvda-roth</v>
+      </c>
+      <c r="B16" t="str">
+        <v>NVIDIA Corp.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NVDA</v>
+      </c>
+      <c r="D16">
+        <v>25</v>
+      </c>
+      <c r="E16">
+        <v>480</v>
+      </c>
+      <c r="F16">
+        <v>892</v>
+      </c>
+      <c r="G16" t="str">
+        <v>High-growth in Roth for tax-free gains. AI thesis.</v>
+      </c>
+      <c r="H16" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J16">
+        <v>12000</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2023-06-20</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>aapl-roth</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B17" t="str">
         <v>Apple Inc.</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C17" t="str">
         <v>AAPL</v>
       </c>
-      <c r="D14">
-        <v>35</v>
-      </c>
-      <c r="E14">
-        <v>180</v>
-      </c>
-      <c r="F14">
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>178</v>
+      </c>
+      <c r="F17">
         <v>242</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G17" t="str">
         <v>Long-term hold in Roth. Tax-free dividend growth.</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H17" t="str">
         <v>roth-ira</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I17" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="J14">
-        <v>6300</v>
-      </c>
-      <c r="K14" t="str">
+      <c r="J17">
+        <v>17800</v>
+      </c>
+      <c r="K17" t="str">
         <v>2023-03-15</v>
       </c>
-      <c r="L14" t="str">
+      <c r="L17" t="str">
         <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L14"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -453,37 +453,37 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>meta</v>
+        <v>vti</v>
       </c>
       <c r="B2" t="str">
-        <v>Meta Platforms</v>
+        <v>Vanguard Total Stock Market ETF</v>
       </c>
       <c r="C2" t="str">
-        <v>META</v>
+        <v>VTI</v>
       </c>
       <c r="D2">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E2">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="F2">
-        <v>595</v>
+        <v>280</v>
       </c>
       <c r="G2" t="str">
-        <v>Vested RSU from 6 years at Meta (E6). Now regular stock. Selling 10-15% annually to diversify. Concentrated position — plan multi-year drawdown.</v>
+        <v>Core diversified holding. Funded by Anthropic tender offer proceeds (2024-2025). Tax-efficient broad market.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>E*TRADE</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J2">
-        <v>450000</v>
+        <v>258000</v>
       </c>
       <c r="K2" t="str">
-        <v>2018-06-01</v>
+        <v>2024-12-01</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
@@ -491,37 +491,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>voo-401k</v>
+        <v>vxus</v>
       </c>
       <c r="B3" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C3" t="str">
-        <v>VOO</v>
+        <v>VXUS</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E3">
-        <v>380</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="G3" t="str">
-        <v>Core 401(k) holding. DCA via payroll. Google matches up to $9,500/yr.</v>
+        <v>International diversification. Foreign tax credit eligible.</v>
       </c>
       <c r="H3" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>Google 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J3">
-        <v>380000</v>
+        <v>78000</v>
       </c>
       <c r="K3" t="str">
-        <v>2020-01-10</v>
+        <v>2024-12-15</v>
       </c>
       <c r="L3" t="str">
         <v>2026-02-12</v>
@@ -529,37 +529,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>vxus-401k</v>
+        <v>qqq</v>
       </c>
       <c r="B4" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Invesco QQQ Trust</v>
       </c>
       <c r="C4" t="str">
-        <v>VXUS</v>
+        <v>QQQ</v>
       </c>
       <c r="D4">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="E4">
-        <v>52</v>
+        <v>385</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>530</v>
       </c>
       <c r="G4" t="str">
-        <v>International diversification in 401(k). ~7% of retirement allocation.</v>
+        <v>Nasdaq-100 exposure. Tech-heavy tilt — comfortable given domain expertise.</v>
       </c>
       <c r="H4" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I4" t="str">
-        <v>Google 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J4">
-        <v>36400</v>
+        <v>96250</v>
       </c>
       <c r="K4" t="str">
-        <v>2020-01-10</v>
+        <v>2025-01-10</v>
       </c>
       <c r="L4" t="str">
         <v>2026-02-12</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bnd-401k</v>
+        <v>bnd</v>
       </c>
       <c r="B5" t="str">
         <v>Vanguard Total Bond Market ETF</v>
@@ -576,7 +576,7 @@
         <v>BND</v>
       </c>
       <c r="D5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E5">
         <v>74</v>
@@ -585,19 +585,19 @@
         <v>72</v>
       </c>
       <c r="G5" t="str">
-        <v>Bond allocation in 401(k). ~7% of retirement. Slight loss from rate hikes.</v>
+        <v>Bond allocation for stability. Slight loss from rate hikes.</v>
       </c>
       <c r="H5" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I5" t="str">
-        <v>Google 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J5">
-        <v>44400</v>
+        <v>37000</v>
       </c>
       <c r="K5" t="str">
-        <v>2021-06-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="L5" t="str">
         <v>2026-02-12</v>
@@ -605,25 +605,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>vti</v>
+        <v>aapl</v>
       </c>
       <c r="B6" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C6" t="str">
-        <v>VTI</v>
+        <v>AAPL</v>
       </c>
       <c r="D6">
-        <v>1800</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="F6">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="G6" t="str">
-        <v>Core diversified holding. Funded partly by META stock sales. Tax-efficient broad market.</v>
+        <v>Long-term conviction hold. On-device AI play.</v>
       </c>
       <c r="H6" t="str">
         <v>taxable</v>
@@ -632,10 +632,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J6">
-        <v>378000</v>
+        <v>27000</v>
       </c>
       <c r="K6" t="str">
-        <v>2022-03-15</v>
+        <v>2024-11-15</v>
       </c>
       <c r="L6" t="str">
         <v>2026-02-12</v>
@@ -643,25 +643,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>qqq</v>
+        <v>nvda</v>
       </c>
       <c r="B7" t="str">
-        <v>Invesco QQQ Trust</v>
+        <v>NVIDIA Corp.</v>
       </c>
       <c r="C7" t="str">
-        <v>QQQ</v>
+        <v>NVDA</v>
       </c>
       <c r="D7">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E7">
-        <v>380</v>
+        <v>49</v>
       </c>
       <c r="F7">
-        <v>530</v>
+        <v>187</v>
       </c>
       <c r="G7" t="str">
-        <v>Nasdaq-100 exposure. Tech-heavy tilt alongside employer stock.</v>
+        <v>AI infrastructure leader. High conviction — understands the compute moat deeply. Post 10:1 split (Jun 2024).</v>
       </c>
       <c r="H7" t="str">
         <v>taxable</v>
@@ -670,10 +670,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J7">
-        <v>152000</v>
+        <v>24500</v>
       </c>
       <c r="K7" t="str">
-        <v>2023-01-20</v>
+        <v>2025-01-20</v>
       </c>
       <c r="L7" t="str">
         <v>2026-02-12</v>
@@ -681,25 +681,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>vxus</v>
+        <v>schd</v>
       </c>
       <c r="B8" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Schwab US Dividend Equity ETF</v>
       </c>
       <c r="C8" t="str">
-        <v>VXUS</v>
+        <v>SCHD</v>
       </c>
       <c r="D8">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>23.33</v>
       </c>
       <c r="F8">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G8" t="str">
-        <v>International diversification in taxable. Foreign tax credit eligible.</v>
+        <v>Dividend ETF for passive income. Diversification from growth tilt. Post 3:1 split (Oct 2024).</v>
       </c>
       <c r="H8" t="str">
         <v>taxable</v>
@@ -708,10 +708,10 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J8">
-        <v>62400</v>
+        <v>20997</v>
       </c>
       <c r="K8" t="str">
-        <v>2022-06-15</v>
+        <v>2025-06-01</v>
       </c>
       <c r="L8" t="str">
         <v>2026-02-12</v>
@@ -719,37 +719,37 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>vgt</v>
+        <v>voo-401k</v>
       </c>
       <c r="B9" t="str">
-        <v>Vanguard Information Technology ETF</v>
+        <v>Vanguard S&amp;P 500 ETF</v>
       </c>
       <c r="C9" t="str">
-        <v>VGT</v>
+        <v>VOO</v>
       </c>
       <c r="D9">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="E9">
-        <v>450</v>
+        <v>385</v>
       </c>
       <c r="F9">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="G9" t="str">
-        <v>Sector bet on tech. Overlaps with employer exposure — consider trimming.</v>
+        <v>Core 401(k) holding. DCA via payroll. No employer match at Anthropic.</v>
       </c>
       <c r="H9" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I9" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity 401(k)</v>
       </c>
       <c r="J9">
-        <v>67500</v>
+        <v>173250</v>
       </c>
       <c r="K9" t="str">
-        <v>2023-06-01</v>
+        <v>2022-02-01</v>
       </c>
       <c r="L9" t="str">
         <v>2026-02-12</v>
@@ -757,37 +757,37 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>aapl</v>
+        <v>vxus-401k</v>
       </c>
       <c r="B10" t="str">
-        <v>Apple Inc.</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C10" t="str">
-        <v>AAPL</v>
+        <v>VXUS</v>
       </c>
       <c r="D10">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E10">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>242</v>
+        <v>60</v>
       </c>
       <c r="G10" t="str">
-        <v>Long-term conviction hold. Services revenue accelerating.</v>
+        <v>International diversification in 401(k).</v>
       </c>
       <c r="H10" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I10" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity 401(k)</v>
       </c>
       <c r="J10">
-        <v>44500</v>
+        <v>20800</v>
       </c>
       <c r="K10" t="str">
-        <v>2023-03-15</v>
+        <v>2022-02-01</v>
       </c>
       <c r="L10" t="str">
         <v>2026-02-12</v>
@@ -795,37 +795,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>nvda</v>
+        <v>bnd-401k</v>
       </c>
       <c r="B11" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Vanguard Total Bond Market ETF</v>
       </c>
       <c r="C11" t="str">
-        <v>NVDA</v>
+        <v>BND</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="E11">
-        <v>480</v>
+        <v>74</v>
       </c>
       <c r="F11">
-        <v>892</v>
+        <v>72</v>
       </c>
       <c r="G11" t="str">
-        <v>AI infrastructure leader. High conviction position.</v>
+        <v>Bond allocation in 401(k). Slight loss from rate hikes.</v>
       </c>
       <c r="H11" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I11" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity 401(k)</v>
       </c>
       <c r="J11">
-        <v>38400</v>
+        <v>44400</v>
       </c>
       <c r="K11" t="str">
-        <v>2023-06-20</v>
+        <v>2022-06-01</v>
       </c>
       <c r="L11" t="str">
         <v>2026-02-12</v>
@@ -833,37 +833,37 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>schd</v>
+        <v>vti-roth</v>
       </c>
       <c r="B12" t="str">
-        <v>Schwab US Dividend Equity ETF</v>
+        <v>Vanguard Total Stock Market ETF</v>
       </c>
       <c r="C12" t="str">
-        <v>SCHD</v>
+        <v>VTI</v>
       </c>
       <c r="D12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="F12">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="G12" t="str">
-        <v>Dividend ETF for passive income. Diversification from growth tilt.</v>
+        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
       </c>
       <c r="H12" t="str">
-        <v>taxable</v>
+        <v>roth-ira</v>
       </c>
       <c r="I12" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity Roth IRA</v>
       </c>
       <c r="J12">
-        <v>35000</v>
+        <v>22500</v>
       </c>
       <c r="K12" t="str">
-        <v>2023-09-01</v>
+        <v>2023-01-15</v>
       </c>
       <c r="L12" t="str">
         <v>2026-02-12</v>
@@ -871,37 +871,37 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>amzn</v>
+        <v>nvda-roth</v>
       </c>
       <c r="B13" t="str">
-        <v>Amazon</v>
+        <v>NVIDIA Corp.</v>
       </c>
       <c r="C13" t="str">
-        <v>AMZN</v>
+        <v>NVDA</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E13">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="F13">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="G13" t="str">
-        <v>AWS margins expanding. Advertising segment growing.</v>
+        <v>High-growth in Roth for tax-free gains. AI thesis. Post 10:1 split (Jun 2024).</v>
       </c>
       <c r="H13" t="str">
-        <v>taxable</v>
+        <v>roth-ira</v>
       </c>
       <c r="I13" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity Roth IRA</v>
       </c>
       <c r="J13">
-        <v>17400</v>
+        <v>7350</v>
       </c>
       <c r="K13" t="str">
-        <v>2023-09-05</v>
+        <v>2023-06-20</v>
       </c>
       <c r="L13" t="str">
         <v>2026-02-12</v>
@@ -909,159 +909,45 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>vnq</v>
+        <v>aapl-roth</v>
       </c>
       <c r="B14" t="str">
-        <v>Vanguard Real Estate ETF</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C14" t="str">
-        <v>VNQ</v>
+        <v>AAPL</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="E14">
-        <v>82.5</v>
+        <v>180</v>
       </c>
       <c r="F14">
-        <v>91.2</v>
+        <v>242</v>
       </c>
       <c r="G14" t="str">
-        <v>Broad REIT exposure. Dividend yield ~3.8%.</v>
+        <v>Long-term hold in Roth. Tax-free dividend growth.</v>
       </c>
       <c r="H14" t="str">
-        <v>taxable</v>
+        <v>roth-ira</v>
       </c>
       <c r="I14" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Fidelity Roth IRA</v>
       </c>
       <c r="J14">
-        <v>16500</v>
+        <v>6300</v>
       </c>
       <c r="K14" t="str">
-        <v>2024-01-15</v>
+        <v>2023-03-15</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>vti-roth</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
-      </c>
-      <c r="C15" t="str">
-        <v>VTI</v>
-      </c>
-      <c r="D15">
-        <v>200</v>
-      </c>
-      <c r="E15">
-        <v>220</v>
-      </c>
-      <c r="F15">
-        <v>280</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
-      </c>
-      <c r="H15" t="str">
-        <v>roth-ira</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Fidelity Roth IRA</v>
-      </c>
-      <c r="J15">
-        <v>44000</v>
-      </c>
-      <c r="K15" t="str">
-        <v>2022-04-15</v>
-      </c>
-      <c r="L15" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>nvda-roth</v>
-      </c>
-      <c r="B16" t="str">
-        <v>NVIDIA Corp.</v>
-      </c>
-      <c r="C16" t="str">
-        <v>NVDA</v>
-      </c>
-      <c r="D16">
-        <v>25</v>
-      </c>
-      <c r="E16">
-        <v>480</v>
-      </c>
-      <c r="F16">
-        <v>892</v>
-      </c>
-      <c r="G16" t="str">
-        <v>High-growth in Roth for tax-free gains. AI thesis.</v>
-      </c>
-      <c r="H16" t="str">
-        <v>roth-ira</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Fidelity Roth IRA</v>
-      </c>
-      <c r="J16">
-        <v>12000</v>
-      </c>
-      <c r="K16" t="str">
-        <v>2023-06-20</v>
-      </c>
-      <c r="L16" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>aapl-roth</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Apple Inc.</v>
-      </c>
-      <c r="C17" t="str">
-        <v>AAPL</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>178</v>
-      </c>
-      <c r="F17">
-        <v>242</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Long-term hold in Roth. Tax-free dividend growth.</v>
-      </c>
-      <c r="H17" t="str">
-        <v>roth-ira</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Fidelity Roth IRA</v>
-      </c>
-      <c r="J17">
-        <v>17800</v>
-      </c>
-      <c r="K17" t="str">
-        <v>2023-03-15</v>
-      </c>
-      <c r="L17" t="str">
         <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -398,20 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L14"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,7 +454,7 @@
         <v>215</v>
       </c>
       <c r="F2">
-        <v>280</v>
+        <v>336.01</v>
       </c>
       <c r="G2" t="str">
         <v>Core diversified holding. Funded by Anthropic tender offer proceeds (2024-2025). Tax-efficient broad market.</v>
@@ -486,7 +472,7 @@
         <v>2024-12-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +492,7 @@
         <v>52</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>82.13</v>
       </c>
       <c r="G3" t="str">
         <v>International diversification. Foreign tax credit eligible.</v>
@@ -524,7 +510,7 @@
         <v>2024-12-15</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +530,7 @@
         <v>385</v>
       </c>
       <c r="F4">
-        <v>530</v>
+        <v>600.64</v>
       </c>
       <c r="G4" t="str">
         <v>Nasdaq-100 exposure. Tech-heavy tilt — comfortable given domain expertise.</v>
@@ -562,7 +548,7 @@
         <v>2025-01-10</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="5">
@@ -582,7 +568,7 @@
         <v>74</v>
       </c>
       <c r="F5">
-        <v>72</v>
+        <v>74.66</v>
       </c>
       <c r="G5" t="str">
         <v>Bond allocation for stability. Slight loss from rate hikes.</v>
@@ -600,7 +586,7 @@
         <v>2025-03-01</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +606,7 @@
         <v>180</v>
       </c>
       <c r="F6">
-        <v>242</v>
+        <v>261.73</v>
       </c>
       <c r="G6" t="str">
         <v>Long-term conviction hold. On-device AI play.</v>
@@ -638,7 +624,7 @@
         <v>2024-11-15</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +644,7 @@
         <v>49</v>
       </c>
       <c r="F7">
-        <v>187</v>
+        <v>186.94</v>
       </c>
       <c r="G7" t="str">
         <v>AI infrastructure leader. High conviction — understands the compute moat deeply. Post 10:1 split (Jun 2024).</v>
@@ -676,7 +662,7 @@
         <v>2025-01-20</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="8">
@@ -696,7 +682,7 @@
         <v>23.33</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>31.34</v>
       </c>
       <c r="G8" t="str">
         <v>Dividend ETF for passive income. Diversification from growth tilt. Post 3:1 split (Oct 2024).</v>
@@ -714,7 +700,7 @@
         <v>2025-06-01</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +720,7 @@
         <v>385</v>
       </c>
       <c r="F9">
-        <v>520</v>
+        <v>626.49</v>
       </c>
       <c r="G9" t="str">
         <v>Core 401(k) holding. DCA via payroll. No employer match at Anthropic.</v>
@@ -752,7 +738,7 @@
         <v>2022-02-01</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="10">
@@ -772,7 +758,7 @@
         <v>52</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>82.13</v>
       </c>
       <c r="G10" t="str">
         <v>International diversification in 401(k).</v>
@@ -790,7 +776,7 @@
         <v>2022-02-01</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="11">
@@ -810,7 +796,7 @@
         <v>74</v>
       </c>
       <c r="F11">
-        <v>72</v>
+        <v>74.66</v>
       </c>
       <c r="G11" t="str">
         <v>Bond allocation in 401(k). Slight loss from rate hikes.</v>
@@ -828,7 +814,7 @@
         <v>2022-06-01</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="12">
@@ -848,7 +834,7 @@
         <v>225</v>
       </c>
       <c r="F12">
-        <v>280</v>
+        <v>336.01</v>
       </c>
       <c r="G12" t="str">
         <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
@@ -866,7 +852,7 @@
         <v>2023-01-15</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="13">
@@ -886,7 +872,7 @@
         <v>49</v>
       </c>
       <c r="F13">
-        <v>187</v>
+        <v>186.94</v>
       </c>
       <c r="G13" t="str">
         <v>High-growth in Roth for tax-free gains. AI thesis. Post 10:1 split (Jun 2024).</v>
@@ -904,7 +890,7 @@
         <v>2023-06-20</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="14">
@@ -924,7 +910,7 @@
         <v>180</v>
       </c>
       <c r="F14">
-        <v>242</v>
+        <v>261.73</v>
       </c>
       <c r="G14" t="str">
         <v>Long-term hold in Roth. Tax-free dividend growth.</v>
@@ -942,7 +928,7 @@
         <v>2023-03-15</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -397,7 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,121 +453,121 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>vti</v>
+        <v>meta</v>
       </c>
       <c r="B2" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
+        <v>Meta Platforms</v>
       </c>
       <c r="C2" t="str">
-        <v>VTI</v>
+        <v>META</v>
       </c>
       <c r="D2">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="E2">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>336.01</v>
+        <v>595</v>
       </c>
       <c r="G2" t="str">
-        <v>Core diversified holding. Funded by Anthropic tender offer proceeds (2024-2025). Tax-efficient broad market.</v>
+        <v>Vested RSU from 6 years at Meta (E6). Now regular stock. Selling 10-15% annually to diversify. Concentrated position — plan multi-year drawdown.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>Schwab Brokerage</v>
+        <v>E*TRADE</v>
       </c>
       <c r="J2">
-        <v>258000</v>
+        <v>450000</v>
       </c>
       <c r="K2" t="str">
-        <v>2024-12-01</v>
+        <v>2018-06-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>vxus</v>
+        <v>voo-401k</v>
       </c>
       <c r="B3" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Vanguard S&amp;P 500 ETF</v>
       </c>
       <c r="C3" t="str">
-        <v>VXUS</v>
+        <v>VOO</v>
       </c>
       <c r="D3">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E3">
-        <v>52</v>
+        <v>380</v>
       </c>
       <c r="F3">
-        <v>82.13</v>
+        <v>520</v>
       </c>
       <c r="G3" t="str">
-        <v>International diversification. Foreign tax credit eligible.</v>
+        <v>Core 401(k) holding. DCA via payroll. Google matches up to $9,500/yr.</v>
       </c>
       <c r="H3" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I3" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J3">
-        <v>78000</v>
+        <v>380000</v>
       </c>
       <c r="K3" t="str">
-        <v>2024-12-15</v>
+        <v>2020-01-10</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>qqq</v>
+        <v>vxus-401k</v>
       </c>
       <c r="B4" t="str">
-        <v>Invesco QQQ Trust</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C4" t="str">
-        <v>QQQ</v>
+        <v>VXUS</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="E4">
-        <v>385</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>600.64</v>
+        <v>60</v>
       </c>
       <c r="G4" t="str">
-        <v>Nasdaq-100 exposure. Tech-heavy tilt — comfortable given domain expertise.</v>
+        <v>International diversification in 401(k). ~7% of retirement allocation.</v>
       </c>
       <c r="H4" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I4" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J4">
-        <v>96250</v>
+        <v>36400</v>
       </c>
       <c r="K4" t="str">
-        <v>2025-01-10</v>
+        <v>2020-01-10</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bnd</v>
+        <v>bnd-401k</v>
       </c>
       <c r="B5" t="str">
         <v>Vanguard Total Bond Market ETF</v>
@@ -562,54 +576,54 @@
         <v>BND</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E5">
         <v>74</v>
       </c>
       <c r="F5">
-        <v>74.66</v>
+        <v>72</v>
       </c>
       <c r="G5" t="str">
-        <v>Bond allocation for stability. Slight loss from rate hikes.</v>
+        <v>Bond allocation in 401(k). ~7% of retirement. Slight loss from rate hikes.</v>
       </c>
       <c r="H5" t="str">
-        <v>taxable</v>
+        <v>traditional-401k</v>
       </c>
       <c r="I5" t="str">
-        <v>Schwab Brokerage</v>
+        <v>Google 401(k)</v>
       </c>
       <c r="J5">
-        <v>37000</v>
+        <v>44400</v>
       </c>
       <c r="K5" t="str">
-        <v>2025-03-01</v>
+        <v>2021-06-01</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>aapl</v>
+        <v>vti</v>
       </c>
       <c r="B6" t="str">
-        <v>Apple Inc.</v>
+        <v>Vanguard Total Stock Market ETF</v>
       </c>
       <c r="C6" t="str">
-        <v>AAPL</v>
+        <v>VTI</v>
       </c>
       <c r="D6">
-        <v>150</v>
+        <v>1800</v>
       </c>
       <c r="E6">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F6">
-        <v>261.73</v>
+        <v>280</v>
       </c>
       <c r="G6" t="str">
-        <v>Long-term conviction hold. On-device AI play.</v>
+        <v>Core diversified holding. Funded partly by META stock sales. Tax-efficient broad market.</v>
       </c>
       <c r="H6" t="str">
         <v>taxable</v>
@@ -618,36 +632,36 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J6">
-        <v>27000</v>
+        <v>378000</v>
       </c>
       <c r="K6" t="str">
-        <v>2024-11-15</v>
+        <v>2022-03-15</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>nvda</v>
+        <v>qqq</v>
       </c>
       <c r="B7" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Invesco QQQ Trust</v>
       </c>
       <c r="C7" t="str">
-        <v>NVDA</v>
+        <v>QQQ</v>
       </c>
       <c r="D7">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>380</v>
       </c>
       <c r="F7">
-        <v>186.94</v>
+        <v>530</v>
       </c>
       <c r="G7" t="str">
-        <v>AI infrastructure leader. High conviction — understands the compute moat deeply. Post 10:1 split (Jun 2024).</v>
+        <v>Nasdaq-100 exposure. Tech-heavy tilt alongside employer stock.</v>
       </c>
       <c r="H7" t="str">
         <v>taxable</v>
@@ -656,36 +670,36 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J7">
-        <v>24500</v>
+        <v>152000</v>
       </c>
       <c r="K7" t="str">
-        <v>2025-01-20</v>
+        <v>2023-01-20</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>schd</v>
+        <v>vxus</v>
       </c>
       <c r="B8" t="str">
-        <v>Schwab US Dividend Equity ETF</v>
+        <v>Vanguard Total Intl Stock ETF</v>
       </c>
       <c r="C8" t="str">
-        <v>SCHD</v>
+        <v>VXUS</v>
       </c>
       <c r="D8">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E8">
-        <v>23.33</v>
+        <v>52</v>
       </c>
       <c r="F8">
-        <v>31.34</v>
+        <v>60</v>
       </c>
       <c r="G8" t="str">
-        <v>Dividend ETF for passive income. Diversification from growth tilt. Post 3:1 split (Oct 2024).</v>
+        <v>International diversification in taxable. Foreign tax credit eligible.</v>
       </c>
       <c r="H8" t="str">
         <v>taxable</v>
@@ -694,246 +708,360 @@
         <v>Schwab Brokerage</v>
       </c>
       <c r="J8">
-        <v>20997</v>
+        <v>62400</v>
       </c>
       <c r="K8" t="str">
-        <v>2025-06-01</v>
+        <v>2022-06-15</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>voo-401k</v>
+        <v>vgt</v>
       </c>
       <c r="B9" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+        <v>Vanguard Information Technology ETF</v>
       </c>
       <c r="C9" t="str">
-        <v>VOO</v>
+        <v>VGT</v>
       </c>
       <c r="D9">
+        <v>150</v>
+      </c>
+      <c r="E9">
         <v>450</v>
       </c>
-      <c r="E9">
-        <v>385</v>
-      </c>
       <c r="F9">
-        <v>626.49</v>
+        <v>580</v>
       </c>
       <c r="G9" t="str">
-        <v>Core 401(k) holding. DCA via payroll. No employer match at Anthropic.</v>
+        <v>Sector bet on tech. Overlaps with employer exposure — consider trimming.</v>
       </c>
       <c r="H9" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I9" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J9">
-        <v>173250</v>
+        <v>67500</v>
       </c>
       <c r="K9" t="str">
-        <v>2022-02-01</v>
+        <v>2023-06-01</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>vxus-401k</v>
+        <v>aapl</v>
       </c>
       <c r="B10" t="str">
-        <v>Vanguard Total Intl Stock ETF</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C10" t="str">
-        <v>VXUS</v>
+        <v>AAPL</v>
       </c>
       <c r="D10">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E10">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="F10">
-        <v>82.13</v>
+        <v>242</v>
       </c>
       <c r="G10" t="str">
-        <v>International diversification in 401(k).</v>
+        <v>Long-term conviction hold. Services revenue accelerating.</v>
       </c>
       <c r="H10" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I10" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J10">
-        <v>20800</v>
+        <v>44500</v>
       </c>
       <c r="K10" t="str">
-        <v>2022-02-01</v>
+        <v>2023-03-15</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bnd-401k</v>
+        <v>nvda</v>
       </c>
       <c r="B11" t="str">
-        <v>Vanguard Total Bond Market ETF</v>
+        <v>NVIDIA Corp.</v>
       </c>
       <c r="C11" t="str">
-        <v>BND</v>
+        <v>NVDA</v>
       </c>
       <c r="D11">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E11">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="F11">
-        <v>74.66</v>
+        <v>187</v>
       </c>
       <c r="G11" t="str">
-        <v>Bond allocation in 401(k). Slight loss from rate hikes.</v>
+        <v>AI infrastructure leader. High conviction position. Post 10:1 split (Jun 2024).</v>
       </c>
       <c r="H11" t="str">
-        <v>traditional-401k</v>
+        <v>taxable</v>
       </c>
       <c r="I11" t="str">
-        <v>Fidelity 401(k)</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J11">
-        <v>44400</v>
+        <v>38400</v>
       </c>
       <c r="K11" t="str">
-        <v>2022-06-01</v>
+        <v>2023-06-20</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>vti-roth</v>
+        <v>schd</v>
       </c>
       <c r="B12" t="str">
-        <v>Vanguard Total Stock Market ETF</v>
+        <v>Schwab US Dividend Equity ETF</v>
       </c>
       <c r="C12" t="str">
-        <v>VTI</v>
+        <v>SCHD</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="E12">
-        <v>225</v>
+        <v>23.33</v>
       </c>
       <c r="F12">
-        <v>336.01</v>
+        <v>31</v>
       </c>
       <c r="G12" t="str">
-        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
+        <v>Dividend ETF for passive income. Diversification from growth tilt. Post 3:1 split (Oct 2024).</v>
       </c>
       <c r="H12" t="str">
-        <v>roth-ira</v>
+        <v>taxable</v>
       </c>
       <c r="I12" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J12">
-        <v>22500</v>
+        <v>34995</v>
       </c>
       <c r="K12" t="str">
-        <v>2023-01-15</v>
+        <v>2023-09-01</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>nvda-roth</v>
+        <v>amzn</v>
       </c>
       <c r="B13" t="str">
-        <v>NVIDIA Corp.</v>
+        <v>Amazon</v>
       </c>
       <c r="C13" t="str">
-        <v>NVDA</v>
+        <v>AMZN</v>
       </c>
       <c r="D13">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="F13">
-        <v>186.94</v>
+        <v>228</v>
       </c>
       <c r="G13" t="str">
-        <v>High-growth in Roth for tax-free gains. AI thesis. Post 10:1 split (Jun 2024).</v>
+        <v>AWS margins expanding. Advertising segment growing.</v>
       </c>
       <c r="H13" t="str">
-        <v>roth-ira</v>
+        <v>taxable</v>
       </c>
       <c r="I13" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>Schwab Brokerage</v>
       </c>
       <c r="J13">
-        <v>7350</v>
+        <v>17400</v>
       </c>
       <c r="K13" t="str">
-        <v>2023-06-20</v>
+        <v>2023-09-05</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>vnq</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Vanguard Real Estate ETF</v>
+      </c>
+      <c r="C14" t="str">
+        <v>VNQ</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>82.5</v>
+      </c>
+      <c r="F14">
+        <v>91.2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Broad REIT exposure. Dividend yield ~3.8%.</v>
+      </c>
+      <c r="H14" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Schwab Brokerage</v>
+      </c>
+      <c r="J14">
+        <v>16500</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>vti-roth</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Vanguard Total Stock Market ETF</v>
+      </c>
+      <c r="C15" t="str">
+        <v>VTI</v>
+      </c>
+      <c r="D15">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>220</v>
+      </c>
+      <c r="F15">
+        <v>280</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Core Roth holding. Tax-free growth. Backdoor Roth contributions.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J15">
+        <v>44000</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2022-04-15</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>nvda-roth</v>
+      </c>
+      <c r="B16" t="str">
+        <v>NVIDIA Corp.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NVDA</v>
+      </c>
+      <c r="D16">
+        <v>250</v>
+      </c>
+      <c r="E16">
+        <v>48</v>
+      </c>
+      <c r="F16">
+        <v>187</v>
+      </c>
+      <c r="G16" t="str">
+        <v>High-growth in Roth for tax-free gains. AI thesis. Post 10:1 split (Jun 2024).</v>
+      </c>
+      <c r="H16" t="str">
+        <v>roth-ira</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="J16">
+        <v>12000</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2023-06-20</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>aapl-roth</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B17" t="str">
         <v>Apple Inc.</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C17" t="str">
         <v>AAPL</v>
       </c>
-      <c r="D14">
-        <v>35</v>
-      </c>
-      <c r="E14">
-        <v>180</v>
-      </c>
-      <c r="F14">
-        <v>261.73</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>178</v>
+      </c>
+      <c r="F17">
+        <v>242</v>
+      </c>
+      <c r="G17" t="str">
         <v>Long-term hold in Roth. Tax-free dividend growth.</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H17" t="str">
         <v>roth-ira</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I17" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="J14">
-        <v>6300</v>
-      </c>
-      <c r="K14" t="str">
+      <c r="J17">
+        <v>17800</v>
+      </c>
+      <c r="K17" t="str">
         <v>2023-03-15</v>
       </c>
-      <c r="L14" t="str">
-        <v>2026-02-13</v>
+      <c r="L17" t="str">
+        <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>